--- a/artfynd/A 23383-2026 artfynd.xlsx
+++ b/artfynd/A 23383-2026 artfynd.xlsx
@@ -2310,7 +2310,7 @@
         <v>136174503</v>
       </c>
       <c r="B16" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 23383-2026 artfynd.xlsx
+++ b/artfynd/A 23383-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ27"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2653,27 +2653,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135819444</v>
+        <v>137201729</v>
       </c>
       <c r="B19" t="n">
-        <v>5202</v>
+        <v>57849</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>102621</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2682,19 +2682,23 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bredänget, Bredänget, Nb</t>
+          <t>BrunBjörn, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>850692</v>
+        <v>850736</v>
       </c>
       <c r="R19" t="n">
-        <v>7370029</v>
+        <v>7369939</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2718,12 +2722,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,27 +2752,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135819444</t>
+          <t>https://artportalen.se/Sighting/137201729</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135819354</v>
+        <v>135819444</v>
       </c>
       <c r="B20" t="n">
-        <v>8452</v>
+        <v>5202</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2766,21 +2780,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2790,10 +2804,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>850709</v>
+        <v>850692</v>
       </c>
       <c r="R20" t="n">
-        <v>7370035</v>
+        <v>7370029</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2851,63 +2865,54 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135819354</t>
+          <t>https://artportalen.se/Sighting/135819444</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135219611</v>
+        <v>135819354</v>
       </c>
       <c r="B21" t="n">
-        <v>99276</v>
+        <v>8452</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bredänget, Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>850687</v>
+        <v>850709</v>
       </c>
       <c r="R21" t="n">
-        <v>7369965</v>
+        <v>7370035</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2931,12 +2936,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2951,24 +2956,24 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135219611</t>
+          <t>https://artportalen.se/Sighting/135819354</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135317367</v>
+        <v>135219611</v>
       </c>
       <c r="B22" t="n">
         <v>99276</v>
@@ -2996,24 +3001,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>BrunBjörn, Nb</t>
+          <t>Bredänget, Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>850736</v>
+        <v>850687</v>
       </c>
       <c r="R22" t="n">
-        <v>7369939</v>
+        <v>7369965</v>
       </c>
       <c r="S22" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3051,31 +3061,30 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135317367</t>
+          <t>https://artportalen.se/Sighting/135219611</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135317389</v>
+        <v>135317367</v>
       </c>
       <c r="B23" t="n">
         <v>99276</v>
@@ -3110,17 +3119,17 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Knärot, Nb</t>
+          <t>BrunBjörn, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>850670</v>
+        <v>850736</v>
       </c>
       <c r="R23" t="n">
-        <v>7369968</v>
+        <v>7369939</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3144,12 +3153,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3176,16 +3185,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135317389</t>
+          <t>https://artportalen.se/Sighting/135317367</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135605684</v>
+        <v>135317389</v>
       </c>
       <c r="B24" t="n">
-        <v>99296</v>
+        <v>99276</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3217,14 +3226,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bredänget, Nb</t>
+          <t>Knärot, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>850739</v>
+        <v>850670</v>
       </c>
       <c r="R24" t="n">
-        <v>7370043</v>
+        <v>7369968</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3251,12 +3260,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3283,16 +3292,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135605684</t>
+          <t>https://artportalen.se/Sighting/135317389</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135718208</v>
+        <v>135605684</v>
       </c>
       <c r="B25" t="n">
-        <v>99314</v>
+        <v>99296</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3318,16 +3327,20 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>850717</v>
+        <v>850739</v>
       </c>
       <c r="R25" t="n">
-        <v>7370051</v>
+        <v>7370043</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3354,22 +3367,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3378,71 +3381,72 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Brjan Xotta</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Brjan Xotta</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135718208</t>
+          <t>https://artportalen.se/Sighting/135605684</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135664430</v>
+        <v>135718208</v>
       </c>
       <c r="B26" t="n">
-        <v>99604</v>
+        <v>99314</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222812</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>BrunBjörn, Nb</t>
+          <t>Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>850736</v>
+        <v>850717</v>
       </c>
       <c r="R26" t="n">
-        <v>7369939</v>
+        <v>7370051</v>
       </c>
       <c r="S26" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3466,22 +3470,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3496,27 +3500,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Brjan Xotta</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Brjan Xotta</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135664430</t>
+          <t>https://artportalen.se/Sighting/135718208</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135664877</v>
+        <v>135664430</v>
       </c>
       <c r="B27" t="n">
-        <v>104047</v>
+        <v>99604</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3524,16 +3528,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>223284</v>
+        <v>222812</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3583,7 +3587,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3593,7 +3597,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3618,6 +3622,118 @@
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135664430</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135664877</v>
+      </c>
+      <c r="B28" t="n">
+        <v>104047</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>BrunBjörn, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>850736</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7369939</v>
+      </c>
+      <c r="S28" t="n">
+        <v>100</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135664877</t>
         </is>
@@ -3651,6 +3767,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23383-2026 artfynd.xlsx
+++ b/artfynd/A 23383-2026 artfynd.xlsx
@@ -2688,7 +2688,7 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>BrunBjörn, Nb</t>
+          <t>Västra Svartbyskogen, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">

--- a/artfynd/A 23383-2026 artfynd.xlsx
+++ b/artfynd/A 23383-2026 artfynd.xlsx
@@ -2656,7 +2656,7 @@
         <v>137201729</v>
       </c>
       <c r="B19" t="n">
-        <v>57849</v>
+        <v>57862</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 23383-2026 artfynd.xlsx
+++ b/artfynd/A 23383-2026 artfynd.xlsx
@@ -2656,7 +2656,7 @@
         <v>137201729</v>
       </c>
       <c r="B19" t="n">
-        <v>57862</v>
+        <v>57864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 23383-2026 artfynd.xlsx
+++ b/artfynd/A 23383-2026 artfynd.xlsx
@@ -2656,7 +2656,7 @@
         <v>137201729</v>
       </c>
       <c r="B19" t="n">
-        <v>57864</v>
+        <v>57874</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 23383-2026 artfynd.xlsx
+++ b/artfynd/A 23383-2026 artfynd.xlsx
@@ -2656,7 +2656,7 @@
         <v>137201729</v>
       </c>
       <c r="B19" t="n">
-        <v>57874</v>
+        <v>57875</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 23383-2026 artfynd.xlsx
+++ b/artfynd/A 23383-2026 artfynd.xlsx
@@ -2656,7 +2656,7 @@
         <v>137201729</v>
       </c>
       <c r="B19" t="n">
-        <v>57875</v>
+        <v>57876</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 23383-2026 artfynd.xlsx
+++ b/artfynd/A 23383-2026 artfynd.xlsx
@@ -2656,7 +2656,7 @@
         <v>137201729</v>
       </c>
       <c r="B19" t="n">
-        <v>57876</v>
+        <v>57879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
